--- a/Testing/KiemThu-IoTech.xlsx
+++ b/Testing/KiemThu-IoTech.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\bao-cao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TMDT_IoT\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E772F-242C-4510-ABEA-CC05D12D229D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -634,10 +634,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -940,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -952,14 +952,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -1701,7 +1701,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="28.8" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
